--- a/output/北塩原村_レビュー対応_第2回.xlsx
+++ b/output/北塩原村_レビュー対応_第2回.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>段落492・表152</t>
+          <t>段落494・表152</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">

--- a/output/北塩原村_レビュー対応_第2回.xlsx
+++ b/output/北塩原村_レビュー対応_第2回.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>この点は村の回答（M-19）が前提であり、当方では着手できない</t>
+          <t>この点は村の回答（Ｍ-19）が前提であり、当方では着手できない</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>村M-22〜M-27、県S-11〜S-13、他メンバーS-14</t>
+          <t>村Ｍ-22〜Ｍ-27、県Ｓ-11〜Ｓ-13、他メンバーＳ-14</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>第5章4に重度障がい者の内数の表（4区分）を新設し、強度行動障害の判定方法（行動関連項目10点以上）を注記した。人数は村への確認（M-22）</t>
+          <t>第5章4に重度障がい者の内数の表（4区分）を新設し、強度行動障害の判定方法（行動関連項目10点以上）を注記した。人数は村への確認（Ｍ-22）</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>対応済み。ただし公表率・更新率100％が県の目標か村の目標かは告示で確定させる（S-7）</t>
+          <t>対応済み。ただし公表率・更新率100％が県の目標か村の目標かは告示で確定させる（Ｓ-7）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>村の回答（M-19）を待って一括で差し替える。他メンバーの素案については、仮置き値であることを本文に明示するか、差し替えまで数値を伏せるかを確認する（S-1）</t>
+          <t>村の回答（Ｍ-19）を待って一括で差し替える。他メンバーの素案については、仮置き値であることを本文に明示するか、差し替えまで数値を伏せるかを確認する（Ｓ-1）</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>他メンバーのワークシートの2シートについて、実調査への差し替えと、未実施の事業者調査の隔離を申し送る（S-8）</t>
+          <t>他メンバーのワークシートの2シートについて、実調査への差し替えと、未実施の事業者調査の隔離を申し送る（Ｓ-8）</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>村への確認（M-21 卒業予定者の一覧、M-18 移行管理台帳）の回答後に第2次算定で積み上げる。表の枠は設置済み</t>
+          <t>村への確認（Ｍ-21 卒業予定者の一覧、Ｍ-18 移行管理台帳）の回答後に第2次算定で積み上げる。表の枠は設置済み</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>記載は対応済み。到達年度ごとの人数は村への確認（M-15）の回答後。介護保険事業計画との突合は別途7シートで整理済み</t>
+          <t>記載は対応済み。到達年度ごとの人数は村への確認（Ｍ-15）の回答後。介護保険事業計画との突合は別途7シートで整理済み</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>第5章4に4区分（強度行動障害・高次脳機能障害・医療的ケア児等・重症心身障害児者）×現在の人数・令和9〜11年度・主に必要となるサービスの表を新設した。人数は村への確認（M-22）。原典（別表第一 三）で努力義務であることを確認した</t>
+          <t>第5章4に4区分（強度行動障害・高次脳機能障害・医療的ケア児等・重症心身障害児者）×現在の人数・令和9〜11年度・主に必要となるサービスの表を新設した。人数は村への確認（Ｍ-22）。原典（別表第一 三）で努力義務であることを確認した</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>第5章8に「中山間・人口減少地域の制度の活用」を新設し、対象地域の基準と運用が示された後に活用の可能性を検討する旨の留保を置いた。法律番号・施行期日は確認事項（S-11）</t>
+          <t>第5章8に「中山間・人口減少地域の制度の活用」を新設し、対象地域の基準と運用が示された後に活用の可能性を検討する旨の留保を置いた。法律番号・施行期日は確認事項（Ｓ-11）</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>3段階で整理し直し、支給決定・計画作成・地域移行・成年後見の4つの場面で本人の意思及び選好を尊重することを基本とした。ガイドライン第2版の確定は確認事項（S-12）</t>
+          <t>3段階で整理し直し、支給決定・計画作成・地域移行・成年後見の4つの場面で本人の意思及び選好を尊重することを基本とした。ガイドライン第2版の確定は確認事項（Ｓ-12）</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>第6章3「制度の見直しへの対応」を新設し、後見・保佐を補助に一元化すること、終身を前提としない運用、本人の意向の把握の明確化を記載した。法律番号・施行期日は確認事項（S-13）</t>
+          <t>第6章3「制度の見直しへの対応」を新設し、後見・保佐を補助に一元化すること、終身を前提としない運用、本人の意向の把握の明確化を記載した。法律番号・施行期日は確認事項（Ｓ-13）</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>目標値0人の根拠を6項目（本人の意向・家族の意向・共同生活援助等の受入れの可能性・医療の継続・夜間の支援体制・地域生活の体験の機会）の確認に基づくものに改め、確認表を新設した。確認結果は村へ照会（M-13・M-23）</t>
+          <t>目標値0人の根拠を6項目（本人の意向・家族の意向・共同生活援助等の受入れの可能性・医療の継続・夜間の支援体制・地域生活の体験の機会）の確認に基づくものに改め、確認表を新設した。確認結果は村へ照会（Ｍ-13・Ｍ-23）</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>計画本文は「令和８年６月に公布された社会福祉法等の一部を改正する法律」と書き、法律番号を入れない。県へ確認（S-11）</t>
+          <t>計画本文は「令和８年６月に公布された社会福祉法等の一部を改正する法律」と書き、法律番号を入れない。県へ確認（Ｓ-11）</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>計画本文は「令和８年６月に民法等の一部を改正する法律が公布され」と書き、法律番号を入れない。村・県へ確認（S-13）</t>
+          <t>計画本文は「令和８年６月に民法等の一部を改正する法律が公布され」と書き、法律番号を入れない。村・県へ確認（Ｓ-13）</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>計画本文は3段階の考え方を書き、確定後に用語を揃える（S-12）</t>
+          <t>計画本文は3段階の考え方を書き、確定後に用語を揃える（Ｓ-12）</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>村の回答待ち（M-19）</t>
+          <t>村の回答待ち（Ｍ-19）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>村照会 M-19</t>
+          <t>村照会 Ｍ-19</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>確認 S-8</t>
+          <t>確認 Ｓ-8</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>第5章2（年齢到達・学校卒業）と第5章4（重度障がい者の内数）の表の枠を設けた。人数は M-18・M-21・M-22 の回答後</t>
+          <t>第5章2（年齢到達・学校卒業）と第5章4（重度障がい者の内数）の表の枠を設けた。人数は Ｍ-18・Ｍ-21・Ｍ-22 の回答後</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>村照会 M-18・M-21・M-22</t>
+          <t>村照会 Ｍ-18・Ｍ-21・Ｍ-22</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>村照会 M-24</t>
+          <t>村照会 Ｍ-24</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>県照会 S-12</t>
+          <t>県照会 Ｓ-12</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>村照会 M-25</t>
+          <t>村照会 Ｍ-25</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2845,7 +2845,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の村照会M-1〜M-21、県照会Q-1〜Q-8、他メンバー・村への確認S-1〜S-10に続けて番号を付しました。</t>
+          <t>既存の村照会Ｍ-1〜Ｍ-21、県照会Q-1〜Q-8、他メンバー・村への確認Ｓ-1〜Ｓ-10に続けて番号を付しました。</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>M-22</t>
+          <t>Ｍ-22</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2906,7 +2906,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>M-23</t>
+          <t>Ｍ-23</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>Ｍ-24</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -2960,7 +2960,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>M-25</t>
+          <t>Ｍ-25</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>Ｍ-26</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>M-27</t>
+          <t>Ｍ-27</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -3041,7 +3041,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -3068,7 +3068,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>S-12</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>S-13</t>
+          <t>Ｓ-13</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -3122,7 +3122,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>S-14</t>
+          <t>Ｓ-14</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
